--- a/todo_list_shiny_userguide.xlsx
+++ b/todo_list_shiny_userguide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\javier\CV\sabatico2024\project\shiny.rrisk\srr_ug\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Greiner\Documents\srr_tutorial\srr_ug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{07397843-BC68-49B5-9F12-B3510FBD2D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870F57D9-DD45-4350-A440-1632A9276C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20520" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Item</t>
   </si>
@@ -60,13 +58,25 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Standard layout</t>
+  </si>
+  <si>
+    <t>.. In Buikldung model</t>
+  </si>
+  <si>
+    <t>Matthuas</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,16 +444,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE3ABBD-2F9A-48EA-85C5-E4C1981F1E1C}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="32.453125" customWidth="1"/>
-    <col min="2" max="2" width="22.81640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" customWidth="1"/>
-    <col min="4" max="4" width="14.6328125" customWidth="1"/>
+    <col min="1" max="1" width="32.5" customWidth="1"/>
+    <col min="2" max="2" width="22.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.375" customWidth="1"/>
+    <col min="4" max="4" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="28.5">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -469,6 +479,20 @@
       </c>
       <c r="D2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/todo_list_shiny_userguide.xlsx
+++ b/todo_list_shiny_userguide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Greiner\Documents\srr_tutorial\srr_ug\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\javier\CV\sabatico2024\project\shiny.rrisk\srr_ug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870F57D9-DD45-4350-A440-1632A9276C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA132FEB-3CB0-4E00-893E-D0EE371A5FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20520" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>Item</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Responsible</t>
   </si>
   <si>
-    <t>Completed</t>
-  </si>
-  <si>
     <t>Fixed Param. &amp; Functions</t>
   </si>
   <si>
@@ -57,9 +54,6 @@
     <t xml:space="preserve">Javier </t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Standard layout</t>
   </si>
   <si>
@@ -69,14 +63,26 @@
     <t>Matthuas</t>
   </si>
   <si>
-    <t>no</t>
+    <t>File working on</t>
+  </si>
+  <si>
+    <t>Waiting</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>_modelcreation.qmd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,55 +450,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE3ABBD-2F9A-48EA-85C5-E4C1981F1E1C}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="32.5" customWidth="1"/>
-    <col min="2" max="2" width="22.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.375" customWidth="1"/>
-    <col min="4" max="4" width="14.625" customWidth="1"/>
+    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" customWidth="1"/>
+    <col min="4" max="4" width="32.453125" customWidth="1"/>
+    <col min="5" max="5" width="22.90625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" ht="28.5">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/todo_list_shiny_userguide.xlsx
+++ b/todo_list_shiny_userguide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\javier\CV\sabatico2024\project\shiny.rrisk\srr_ug\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Greiner\Documents\srr_tutorial\srr_ug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA132FEB-3CB0-4E00-893E-D0EE371A5FBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12863BEF-23E0-46D9-9D14-9B267C9FFB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20520" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>Item</t>
   </si>
@@ -54,15 +54,6 @@
     <t xml:space="preserve">Javier </t>
   </si>
   <si>
-    <t>Standard layout</t>
-  </si>
-  <si>
-    <t>.. In Buikldung model</t>
-  </si>
-  <si>
-    <t>Matthuas</t>
-  </si>
-  <si>
     <t>File working on</t>
   </si>
   <si>
@@ -76,13 +67,37 @@
   </si>
   <si>
     <t>_modelcreation.qmd</t>
+  </si>
+  <si>
+    <t>Standard layout in several parts</t>
+  </si>
+  <si>
+    <t>Matthias</t>
+  </si>
+  <si>
+    <t>_simulation.qmd</t>
+  </si>
+  <si>
+    <t>_documenting_reporting.qmd</t>
+  </si>
+  <si>
+    <t>external word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fixed parameters and functions (Yersinial growth example? </t>
+  </si>
+  <si>
+    <t>Standard layout in several parts, adding little text to monte carlo vs lhc</t>
+  </si>
+  <si>
+    <t>Standard layout in several parts, sigma dist, create better structure for readme distributions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -450,25 +465,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE3ABBD-2F9A-48EA-85C5-E4C1981F1E1C}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
-    <col min="2" max="2" width="29.1796875" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" customWidth="1"/>
-    <col min="4" max="4" width="32.453125" customWidth="1"/>
-    <col min="5" max="5" width="22.90625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="29.125" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="4" max="4" width="32.5" customWidth="1"/>
+    <col min="5" max="5" width="22.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -477,15 +492,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="28.5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -494,21 +509,61 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/todo_list_shiny_userguide.xlsx
+++ b/todo_list_shiny_userguide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Greiner\Documents\srr_tutorial\srr_ug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12863BEF-23E0-46D9-9D14-9B267C9FFB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE1B365-C7EE-4F09-AED4-EDF65E3644A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20520" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
   </bookViews>

--- a/todo_list_shiny_userguide.xlsx
+++ b/todo_list_shiny_userguide.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Greiner\Documents\srr_tutorial\srr_ug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE1B365-C7EE-4F09-AED4-EDF65E3644A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8E2189-BF96-48CF-988E-5A8F34AFB778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20520" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>Item</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Standard layout in several parts, sigma dist, create better structure for readme distributions</t>
+  </si>
+  <si>
+    <t>Please review the update; also note the termionology for replicates instead of MoinetCarlo iterations</t>
   </si>
 </sst>
 </file>
@@ -465,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAE3ABBD-2F9A-48EA-85C5-E4C1981F1E1C}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -566,6 +569,20 @@
         <v>16</v>
       </c>
     </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/todo_list_shiny_userguide.xlsx
+++ b/todo_list_shiny_userguide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Greiner\Documents\srr_tutorial\srr_ug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8E2189-BF96-48CF-988E-5A8F34AFB778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C94DAD83-08AA-40A1-9131-AD1DD436BD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="20520" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17070" xr2:uid="{DA3AE3E0-2FE6-4568-A464-5696C988DC7A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>Item</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>Please review the update; also note the termionology for replicates instead of MoinetCarlo iterations</t>
+  </si>
+  <si>
+    <t>Closed</t>
   </si>
 </sst>
 </file>
@@ -535,7 +538,7 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
